--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/06_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/06_NovatedApp_Regression.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3936495A-1611-4DB6-ABC0-99F6B2D9A6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A2F77D-19BE-496C-A7DB-A53607EC15A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="142">
   <si>
     <t>TC ID</t>
   </si>
@@ -197,85 +197,291 @@
     <t>New Fuel Card</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>30/10/1997</t>
-  </si>
-  <si>
-    <t>0499999999</t>
-  </si>
-  <si>
-    <t>visionpro101@gmail.com.test</t>
-  </si>
-  <si>
     <t>Your Residential Address *</t>
   </si>
   <si>
+    <t>${TC001.Fuel Provider}</t>
+  </si>
+  <si>
+    <t>${TC001.Delivery Address}</t>
+  </si>
+  <si>
+    <t>${TC001.Request Submission Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Last Update Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Request Subtype}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Salutation}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver First Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Last Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Date of Birth}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Mobile Phone}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Email}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Your Residential Address}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Employer Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle}</t>
+  </si>
+  <si>
+    <t>Lease End Date Updated</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Status1</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Registration State</t>
+  </si>
+  <si>
+    <t>Updated By1</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Assigned To1</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>Reason for replacement</t>
+  </si>
+  <si>
+    <t>Fuel Card Number</t>
+  </si>
+  <si>
+    <t>Delivery Address *</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Milne</t>
+  </si>
+  <si>
+    <t>05/06/1995</t>
+  </si>
+  <si>
+    <t>0469750861</t>
+  </si>
+  <si>
+    <t>josh.milne1988@gmail.com.test</t>
+  </si>
+  <si>
+    <t>Test Employer</t>
+  </si>
+  <si>
+    <t>EXB72A</t>
+  </si>
+  <si>
+    <t>FORD RANGER</t>
+  </si>
+  <si>
+    <t>17 Aug 2026</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>Auto Lease</t>
+  </si>
+  <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
+    <t>Joshua Milne</t>
+  </si>
+  <si>
+    <t>${TC001.Claim Type}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle number}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle name}</t>
+  </si>
+  <si>
+    <t>${TC001.Lease End Date}</t>
+  </si>
+  <si>
+    <t>${TC001.Lease End Date Updated}</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damaged </t>
+  </si>
+  <si>
+    <t>REQ-867</t>
+  </si>
+  <si>
+    <t>26 May 2026 09:25 PM</t>
+  </si>
+  <si>
+    <t>Replacement</t>
+  </si>
+  <si>
+    <t>6002300065394875</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>${TC003.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC003.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC003.Claim Type}</t>
+  </si>
+  <si>
+    <t>${TC003.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Odometer}</t>
+  </si>
+  <si>
+    <t>${TC003.Fuel Provider}</t>
+  </si>
+  <si>
+    <t>${TC003.Delivery Address}</t>
+  </si>
+  <si>
+    <t>${TC003.Request Submission Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Update Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Request Subtype}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Salutation}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver First Name}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Last Name}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Name}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Date of Birth}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Mobile Phone}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Email}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Your Residential Address}</t>
+  </si>
+  <si>
+    <t>${TC003.Driver Employer Name}</t>
+  </si>
+  <si>
+    <t>${TC003.Vehicle}</t>
+  </si>
+  <si>
+    <t>${TC003.Vehicle number}</t>
+  </si>
+  <si>
+    <t>${TC003.Vehicle name}</t>
+  </si>
+  <si>
+    <t>${TC003.Lease End Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Lease End Date Updated}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stolen </t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>${TC001.Fuel Provider}</t>
-  </si>
-  <si>
-    <t>${TC001.Delivery Address}</t>
-  </si>
-  <si>
-    <t>${TC001.Request Submission Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Last Update Date}</t>
-  </si>
-  <si>
-    <t>${TC001.Request Subtype}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Salutation}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver First Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Last Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Date of Birth}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Mobile Phone}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Email}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Your Residential Address}</t>
-  </si>
-  <si>
-    <t>${TC001.Driver Employer Name}</t>
-  </si>
-  <si>
-    <t>${TC001.Vehicle}</t>
+    <t>REQ-875</t>
+  </si>
+  <si>
+    <t>Fuel Card Cancellation</t>
+  </si>
+  <si>
+    <t>27 May 2026 02:36 PM</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="165" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,6 +497,20 @@
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF221A15"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -334,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,9 +571,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,10 +882,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:BB5"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:42" s="1" customFormat="1" ht="81" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:54" s="1" customFormat="1" ht="81" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -758,7 +991,7 @@
       <c r="AI1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>47</v>
       </c>
       <c r="AK1" s="6" t="s">
@@ -774,13 +1007,49 @@
         <v>51</v>
       </c>
       <c r="AO1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>35</v>
       </c>
+      <c r="AR1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="2" spans="1:42" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:54" s="2" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
@@ -788,15 +1057,17 @@
         <v>52</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <f>C2+1</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <f>D2</f>
-        <v>1</v>
-      </c>
-      <c r="F2" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
@@ -826,10 +1097,14 @@
       <c r="Q2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="3"/>
+      <c r="R2" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="U2" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="V2" s="5" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
         <v>1 km</v>
@@ -837,55 +1112,102 @@
       <c r="W2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
+      <c r="X2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="AA2" s="5" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="AB2" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AD2" s="5" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="AE2" s="5" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>David Stewart</v>
+        <v>Joshua Milne</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="AG2" s="5" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="AH2" s="5" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="AI2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="AJ2" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="AK2" s="5" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5" t="s">
+        <v>FORD RANGER - EXB72A</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2" s="10" t="str">
+        <f>TEXT(AN2,"dd/mm/yyyy")</f>
+        <v>17/08/2026</v>
+      </c>
+      <c r="AP2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AP2" s="5" t="s">
+      <c r="AQ2" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="AR2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS2" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AT2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AZ2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA2" s="11"/>
+      <c r="BB2" t="s" s="0">
+        <v>106</v>
+      </c>
     </row>
-    <row r="3" spans="1:42" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:54" s="2" customFormat="1" ht="81" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -899,7 +1221,9 @@
       <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
@@ -929,8 +1253,8 @@
       <c r="Q3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>23</v>
+      <c r="R3" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>27</v>
@@ -945,62 +1269,420 @@
         <v>30</v>
       </c>
       <c r="W3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AF3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK3" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="AL3" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS3" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA3" s="11"/>
+      <c r="BB3" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4" t="n">
+        <f>C4+1</f>
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <f>D4</f>
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="V4" s="5" t="str">
+        <f>TEXT(E4,"#,##0")&amp;" km"</f>
+        <v>1 km</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE4" s="5" t="str">
+        <f>_xlfn.CONCAT(AC4," ",AD4)</f>
+        <v>Joshua Milne</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK4" s="5" t="str">
+        <f>AM4&amp;" - "&amp;AL4</f>
+        <v>FORD RANGER - EXB72A</v>
+      </c>
+      <c r="AL4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO4" s="10" t="str">
+        <f>TEXT(AN4,"dd/mm/yyyy")</f>
+        <v>17/08/2026</v>
+      </c>
+      <c r="AP4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AS4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AZ4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB4" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" ht="81" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AZ5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB5" t="s" s="0">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/06_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/06_NovatedApp_Regression.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A2F77D-19BE-496C-A7DB-A53607EC15A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1788E092-EED3-4A7E-A405-883C39CC2D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="145">
   <si>
     <t>TC ID</t>
   </si>
@@ -459,6 +459,15 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>05 Jun 1995</t>
+  </si>
+  <si>
+    <t>FTV21M</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1147,7 @@
         <v>Joshua Milne</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="AG2" s="5" t="s">
         <v>86</v>
@@ -1154,13 +1163,13 @@
       </c>
       <c r="AK2" s="5" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>FORD RANGER - EXB72A</v>
+        <v>MAZDA CX-5 - FTV21M</v>
       </c>
       <c r="AL2" s="5" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="AM2" s="9" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="AN2" s="10" t="s">
         <v>91</v>
